--- a/artfynd/A 53276-2023 artfynd.xlsx
+++ b/artfynd/A 53276-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -796,6 +796,126 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>127728096</v>
+      </c>
+      <c r="B3" t="n">
+        <v>58520</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>208249</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Vanlig groda</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Rana temporaria</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>årsunge</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Hallersrud, Hallersrud, Vrm</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>416656</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6577294</v>
+      </c>
+      <c r="S3" t="n">
+        <v>14</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Hammarö</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Hammarö</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2025-08-21</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>18:28</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2025-08-21</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>18:28</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Åsa Duell</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Åsa Duell</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 53276-2023 artfynd.xlsx
+++ b/artfynd/A 53276-2023 artfynd.xlsx
@@ -802,7 +802,7 @@
         <v>127728096</v>
       </c>
       <c r="B3" t="n">
-        <v>58520</v>
+        <v>58522</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 53276-2023 artfynd.xlsx
+++ b/artfynd/A 53276-2023 artfynd.xlsx
@@ -802,7 +802,7 @@
         <v>127728096</v>
       </c>
       <c r="B3" t="n">
-        <v>58522</v>
+        <v>58525</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 53276-2023 artfynd.xlsx
+++ b/artfynd/A 53276-2023 artfynd.xlsx
@@ -802,7 +802,7 @@
         <v>127728096</v>
       </c>
       <c r="B3" t="n">
-        <v>58525</v>
+        <v>58531</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 53276-2023 artfynd.xlsx
+++ b/artfynd/A 53276-2023 artfynd.xlsx
@@ -802,7 +802,7 @@
         <v>127728096</v>
       </c>
       <c r="B3" t="n">
-        <v>58531</v>
+        <v>58532</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 53276-2023 artfynd.xlsx
+++ b/artfynd/A 53276-2023 artfynd.xlsx
@@ -802,7 +802,7 @@
         <v>127728096</v>
       </c>
       <c r="B3" t="n">
-        <v>58532</v>
+        <v>58543</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 53276-2023 artfynd.xlsx
+++ b/artfynd/A 53276-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>117391073</v>
+        <v>127728096</v>
       </c>
       <c r="B2" t="n">
-        <v>57765</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58817</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100058</v>
+        <v>208249</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Mindre flugsnappare</t>
+          <t>Vanlig groda</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Ficedula parva</t>
+          <t>Rana temporaria</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Bechstein, 1794)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -713,27 +708,28 @@
           <t>1</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>årsunge</t>
+        </is>
+      </c>
       <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+      <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Hallersrud, Vrm</t>
+          <t>Hallersrud, Hallersrud, Vrm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>416737</v>
+        <v>416656</v>
       </c>
       <c r="R2" t="n">
-        <v>6577283</v>
+        <v>6577294</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -757,22 +753,22 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2024-05-30</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>08:32</t>
+          <t>18:28</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2024-05-30</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>08:32</t>
+          <t>18:28</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,135 +783,15 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Kaj Sundström</t>
+          <t>Åsa Duell</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Kaj Sundström</t>
+          <t>Åsa Duell</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
-    </row>
-    <row r="3">
-      <c r="A3" t="n">
-        <v>127728096</v>
-      </c>
-      <c r="B3" t="n">
-        <v>58543</v>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E3" t="n">
-        <v>208249</v>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>Vanlig groda</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>Rana temporaria</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>årsunge</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t>Hallersrud, Hallersrud, Vrm</t>
-        </is>
-      </c>
-      <c r="Q3" t="n">
-        <v>416656</v>
-      </c>
-      <c r="R3" t="n">
-        <v>6577294</v>
-      </c>
-      <c r="S3" t="n">
-        <v>14</v>
-      </c>
-      <c r="T3" t="inlineStr">
-        <is>
-          <t>Värmland</t>
-        </is>
-      </c>
-      <c r="U3" t="inlineStr">
-        <is>
-          <t>Hammarö</t>
-        </is>
-      </c>
-      <c r="V3" t="inlineStr">
-        <is>
-          <t>Värmland</t>
-        </is>
-      </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>Hammarö</t>
-        </is>
-      </c>
-      <c r="Y3" t="inlineStr">
-        <is>
-          <t>2025-08-21</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>18:28</t>
-        </is>
-      </c>
-      <c r="AA3" t="inlineStr">
-        <is>
-          <t>2025-08-21</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>18:28</t>
-        </is>
-      </c>
-      <c r="AD3" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE3" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG3" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT3" t="inlineStr"/>
-      <c r="AW3" t="inlineStr">
-        <is>
-          <t>Åsa Duell</t>
-        </is>
-      </c>
-      <c r="AX3" t="inlineStr">
-        <is>
-          <t>Åsa Duell</t>
-        </is>
-      </c>
-      <c r="AY3" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 53276-2023 artfynd.xlsx
+++ b/artfynd/A 53276-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AZ2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -792,8 +797,16 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127728096</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>